--- a/서울_4반_5조.xlsx
+++ b/서울_4반_5조.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\vibecoding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C3205B-B5E4-4724-84F1-B98A4D023A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A34647-2C9F-4D5F-9C95-ED2684DE07DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="393">
   <si>
     <t>실습 소재</t>
   </si>
@@ -8366,6 +8366,9 @@
   <si>
     <t>한 단계씩</t>
     <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>예정</t>
   </si>
 </sst>
 </file>
@@ -8375,7 +8378,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="&quot;Day &quot;0"/>
   </numFmts>
-  <fonts count="49">
+  <fonts count="50">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8717,8 +8720,16 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8815,6 +8826,11 @@
         <bgColor rgb="FF222222"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -8886,10 +8902,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -8972,6 +8991,25 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -9018,10 +9056,28 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9032,42 +9088,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9105,33 +9125,36 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="17" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="좋음" xfId="1" builtinId="26"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -9429,10 +9452,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="36"/>
+      <c r="C2" s="43"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -9467,10 +9490,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="33"/>
+      <c r="C9" s="40"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -9521,28 +9544,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="35"/>
+      <c r="C17" s="42"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="38"/>
+      <c r="C18" s="45"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="31"/>
+      <c r="C19" s="38"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="31"/>
+      <c r="C20" s="38"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -9576,13 +9599,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
       <c r="B4" s="6" t="s">
@@ -9674,46 +9697,46 @@
     </row>
     <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="33"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="40"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9746,22 +9769,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="52" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="33"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" spans="2:6" ht="35.65" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -9790,784 +9813,784 @@
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="2:6" ht="30" customHeight="1">
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="78" t="s">
+      <c r="C6" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="78" t="s">
+      <c r="E6" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="F6" s="78" t="s">
+      <c r="F6" s="31" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="30" customHeight="1">
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C7" s="78" t="s">
+      <c r="C7" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="78" t="s">
+      <c r="D7" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="78" t="s">
+      <c r="E7" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="F7" s="78" t="s">
+      <c r="F7" s="31" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="30" customHeight="1">
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C8" s="78" t="s">
+      <c r="C8" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="D8" s="78" t="s">
+      <c r="D8" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="E8" s="78" t="s">
+      <c r="E8" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="F8" s="78" t="s">
+      <c r="F8" s="31" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="30" customHeight="1">
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C9" s="78" t="s">
+      <c r="C9" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="78" t="s">
+      <c r="D9" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="E9" s="78" t="s">
+      <c r="E9" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="F9" s="78" t="s">
+      <c r="F9" s="31" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="30" customHeight="1">
-      <c r="B10" s="78" t="s">
+      <c r="B10" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="78" t="s">
+      <c r="C10" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="D10" s="78" t="s">
+      <c r="D10" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="E10" s="78" t="s">
+      <c r="E10" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="F10" s="78" t="s">
+      <c r="F10" s="31" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="30" customHeight="1">
-      <c r="B11" s="78" t="s">
+      <c r="B11" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C11" s="78" t="s">
+      <c r="C11" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="78" t="s">
+      <c r="D11" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="E11" s="78" t="s">
+      <c r="E11" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="F11" s="78" t="s">
+      <c r="F11" s="31" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1">
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="78" t="s">
+      <c r="C12" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="78" t="s">
+      <c r="D12" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="E12" s="78" t="s">
+      <c r="E12" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="F12" s="78" t="s">
+      <c r="F12" s="31" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="30" customHeight="1">
-      <c r="B13" s="78" t="s">
+      <c r="B13" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C13" s="78" t="s">
+      <c r="C13" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="D13" s="78" t="s">
+      <c r="D13" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="E13" s="78" t="s">
+      <c r="E13" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="F13" s="78" t="s">
+      <c r="F13" s="31" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="30" customHeight="1">
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="78" t="s">
+      <c r="C14" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="D14" s="78" t="s">
+      <c r="D14" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="E14" s="78" t="s">
+      <c r="E14" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="F14" s="78" t="s">
+      <c r="F14" s="31" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="30" customHeight="1">
-      <c r="B15" s="78" t="s">
+      <c r="B15" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="78" t="s">
+      <c r="C15" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="D15" s="78" t="s">
+      <c r="D15" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="E15" s="78" t="s">
+      <c r="E15" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="F15" s="78" t="s">
+      <c r="F15" s="31" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="30" customHeight="1">
-      <c r="B16" s="78" t="s">
+      <c r="B16" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="78" t="s">
+      <c r="C16" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="D16" s="78" t="s">
+      <c r="D16" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="E16" s="78" t="s">
+      <c r="E16" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="F16" s="78" t="s">
+      <c r="F16" s="31" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="30" customHeight="1">
-      <c r="B17" s="78" t="s">
+      <c r="B17" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C17" s="78" t="s">
+      <c r="C17" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="D17" s="78" t="s">
+      <c r="D17" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="E17" s="78" t="s">
+      <c r="E17" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="F17" s="78" t="s">
+      <c r="F17" s="31" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="30" customHeight="1">
-      <c r="B18" s="78" t="s">
+      <c r="B18" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="78" t="s">
+      <c r="C18" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="D18" s="78" t="s">
+      <c r="D18" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="E18" s="78" t="s">
+      <c r="E18" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="F18" s="78" t="s">
+      <c r="F18" s="31" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="30" customHeight="1">
-      <c r="B19" s="78" t="s">
+      <c r="B19" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C19" s="78" t="s">
+      <c r="C19" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="D19" s="78" t="s">
+      <c r="D19" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="E19" s="78" t="s">
+      <c r="E19" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="F19" s="78" t="s">
+      <c r="F19" s="31" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="30" customHeight="1">
-      <c r="B20" s="78" t="s">
+      <c r="B20" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C20" s="78" t="s">
+      <c r="C20" s="31" t="s">
         <v>203</v>
       </c>
-      <c r="D20" s="78" t="s">
+      <c r="D20" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="E20" s="78" t="s">
+      <c r="E20" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="F20" s="78" t="s">
+      <c r="F20" s="31" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="30" customHeight="1">
-      <c r="B21" s="78" t="s">
+      <c r="B21" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C21" s="78" t="s">
+      <c r="C21" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="D21" s="78" t="s">
+      <c r="D21" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="E21" s="78" t="s">
+      <c r="E21" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="F21" s="78" t="s">
+      <c r="F21" s="31" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="30" customHeight="1">
-      <c r="B22" s="78" t="s">
+      <c r="B22" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="78" t="s">
+      <c r="C22" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="D22" s="78" t="s">
+      <c r="D22" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="E22" s="78" t="s">
+      <c r="E22" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="F22" s="78" t="s">
+      <c r="F22" s="31" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="30" customHeight="1">
-      <c r="B23" s="78" t="s">
+      <c r="B23" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C23" s="78" t="s">
+      <c r="C23" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="D23" s="78" t="s">
+      <c r="D23" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="E23" s="78" t="s">
+      <c r="E23" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="F23" s="78" t="s">
+      <c r="F23" s="31" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="30" customHeight="1">
-      <c r="B24" s="78" t="s">
+      <c r="B24" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C24" s="78" t="s">
+      <c r="C24" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="D24" s="78" t="s">
+      <c r="D24" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="E24" s="78" t="s">
+      <c r="E24" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="F24" s="78" t="s">
+      <c r="F24" s="31" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="30" customHeight="1">
-      <c r="B25" s="78" t="s">
+      <c r="B25" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C25" s="78" t="s">
+      <c r="C25" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="D25" s="78" t="s">
+      <c r="D25" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="E25" s="78" t="s">
+      <c r="E25" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="F25" s="78" t="s">
+      <c r="F25" s="31" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="30" customHeight="1">
-      <c r="B26" s="78" t="s">
+      <c r="B26" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C26" s="78" t="s">
+      <c r="C26" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="D26" s="78" t="s">
+      <c r="D26" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="E26" s="78" t="s">
+      <c r="E26" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="F26" s="78" t="s">
+      <c r="F26" s="31" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="30" customHeight="1">
-      <c r="B27" s="78" t="s">
+      <c r="B27" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C27" s="78" t="s">
+      <c r="C27" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="D27" s="78" t="s">
+      <c r="D27" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="E27" s="78" t="s">
+      <c r="E27" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="F27" s="78" t="s">
+      <c r="F27" s="31" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="30" customHeight="1">
-      <c r="B28" s="78" t="s">
+      <c r="B28" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C28" s="78" t="s">
+      <c r="C28" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="78" t="s">
+      <c r="D28" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="E28" s="78" t="s">
+      <c r="E28" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="F28" s="78" t="s">
+      <c r="F28" s="31" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="30" customHeight="1">
-      <c r="B29" s="78" t="s">
+      <c r="B29" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C29" s="78" t="s">
+      <c r="C29" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="D29" s="78" t="s">
+      <c r="D29" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="E29" s="78" t="s">
+      <c r="E29" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="F29" s="78" t="s">
+      <c r="F29" s="31" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="30" spans="2:6" ht="30" customHeight="1">
-      <c r="B30" s="78" t="s">
+      <c r="B30" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C30" s="78" t="s">
+      <c r="C30" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="D30" s="78" t="s">
+      <c r="D30" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="E30" s="78" t="s">
+      <c r="E30" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="F30" s="78" t="s">
+      <c r="F30" s="31" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="30" customHeight="1">
-      <c r="B31" s="78" t="s">
+      <c r="B31" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C31" s="78" t="s">
+      <c r="C31" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="D31" s="78" t="s">
+      <c r="D31" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="E31" s="78" t="s">
+      <c r="E31" s="31" t="s">
         <v>243</v>
       </c>
-      <c r="F31" s="78" t="s">
+      <c r="F31" s="31" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="32" spans="2:6" ht="30" customHeight="1">
-      <c r="B32" s="78" t="s">
+      <c r="B32" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C32" s="78" t="s">
+      <c r="C32" s="31" t="s">
         <v>245</v>
       </c>
-      <c r="D32" s="78" t="s">
+      <c r="D32" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="E32" s="78" t="s">
+      <c r="E32" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="F32" s="78" t="s">
+      <c r="F32" s="31" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="33" spans="2:6" ht="30" customHeight="1">
-      <c r="B33" s="78" t="s">
+      <c r="B33" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C33" s="78" t="s">
+      <c r="C33" s="31" t="s">
         <v>249</v>
       </c>
-      <c r="D33" s="78" t="s">
+      <c r="D33" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="E33" s="78" t="s">
+      <c r="E33" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="F33" s="78" t="s">
+      <c r="F33" s="31" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="30" customHeight="1">
-      <c r="B34" s="78" t="s">
+      <c r="B34" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="78" t="s">
+      <c r="C34" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="D34" s="78" t="s">
+      <c r="D34" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="E34" s="78" t="s">
+      <c r="E34" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="F34" s="78" t="s">
+      <c r="F34" s="31" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="35" spans="2:6" ht="30" customHeight="1">
-      <c r="B35" s="78" t="s">
+      <c r="B35" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C35" s="78" t="s">
+      <c r="C35" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="D35" s="78" t="s">
+      <c r="D35" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="E35" s="78" t="s">
+      <c r="E35" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="F35" s="78" t="s">
+      <c r="F35" s="31" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="36" spans="2:6" ht="30" customHeight="1">
-      <c r="B36" s="78" t="s">
+      <c r="B36" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C36" s="78" t="s">
+      <c r="C36" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="D36" s="78" t="s">
+      <c r="D36" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="E36" s="78" t="s">
+      <c r="E36" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="F36" s="78" t="s">
+      <c r="F36" s="31" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="30" customHeight="1">
-      <c r="B37" s="78" t="s">
+      <c r="B37" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="C37" s="78" t="s">
+      <c r="C37" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="D37" s="78" t="s">
+      <c r="D37" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="E37" s="78" t="s">
+      <c r="E37" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="F37" s="78" t="s">
+      <c r="F37" s="31" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="38" spans="2:6" ht="30" customHeight="1">
-      <c r="B38" s="78" t="s">
+      <c r="B38" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="C38" s="78" t="s">
+      <c r="C38" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="D38" s="78" t="s">
+      <c r="D38" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="E38" s="78" t="s">
+      <c r="E38" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="F38" s="78" t="s">
+      <c r="F38" s="31" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="39" spans="2:6" ht="30" customHeight="1">
-      <c r="B39" s="78" t="s">
+      <c r="B39" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="C39" s="78" t="s">
+      <c r="C39" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="D39" s="78" t="s">
+      <c r="D39" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="E39" s="78" t="s">
+      <c r="E39" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="F39" s="78" t="s">
+      <c r="F39" s="31" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="40" spans="2:6" ht="30" customHeight="1">
-      <c r="B40" s="78" t="s">
+      <c r="B40" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="C40" s="78" t="s">
+      <c r="C40" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="D40" s="78" t="s">
+      <c r="D40" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="E40" s="78" t="s">
+      <c r="E40" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="F40" s="78" t="s">
+      <c r="F40" s="31" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="41" spans="2:6" ht="30" customHeight="1">
-      <c r="B41" s="78" t="s">
+      <c r="B41" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="C41" s="78" t="s">
+      <c r="C41" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="D41" s="78" t="s">
+      <c r="D41" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="E41" s="78" t="s">
+      <c r="E41" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="F41" s="78" t="s">
+      <c r="F41" s="31" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="30" customHeight="1">
-      <c r="B42" s="78" t="s">
+      <c r="B42" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="C42" s="78" t="s">
+      <c r="C42" s="31" t="s">
         <v>278</v>
       </c>
-      <c r="D42" s="78" t="s">
+      <c r="D42" s="31" t="s">
         <v>279</v>
       </c>
-      <c r="E42" s="78" t="s">
+      <c r="E42" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="F42" s="78" t="s">
+      <c r="F42" s="31" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="30" customHeight="1">
-      <c r="B43" s="78" t="s">
+      <c r="B43" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="C43" s="78" t="s">
+      <c r="C43" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="D43" s="78" t="s">
+      <c r="D43" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="E43" s="78" t="s">
+      <c r="E43" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="F43" s="78" t="s">
+      <c r="F43" s="31" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="30" customHeight="1">
-      <c r="B44" s="78" t="s">
+      <c r="B44" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="C44" s="78" t="s">
+      <c r="C44" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="D44" s="78" t="s">
+      <c r="D44" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="E44" s="78" t="s">
+      <c r="E44" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="F44" s="78" t="s">
+      <c r="F44" s="31" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="45" spans="2:6" ht="30" customHeight="1">
-      <c r="B45" s="78" t="s">
+      <c r="B45" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="C45" s="78" t="s">
+      <c r="C45" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="D45" s="78" t="s">
+      <c r="D45" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="E45" s="78" t="s">
+      <c r="E45" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="F45" s="78" t="s">
+      <c r="F45" s="31" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="46" spans="2:6" ht="30" customHeight="1">
-      <c r="B46" s="78" t="s">
+      <c r="B46" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C46" s="78" t="s">
+      <c r="C46" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="D46" s="78" t="s">
+      <c r="D46" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="E46" s="78" t="s">
+      <c r="E46" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="F46" s="78" t="s">
+      <c r="F46" s="31" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="47" spans="2:6" ht="30" customHeight="1">
-      <c r="B47" s="78" t="s">
+      <c r="B47" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C47" s="78" t="s">
+      <c r="C47" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="D47" s="78" t="s">
+      <c r="D47" s="31" t="s">
         <v>294</v>
       </c>
-      <c r="E47" s="78" t="s">
+      <c r="E47" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="F47" s="78" t="s">
+      <c r="F47" s="31" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="48" spans="2:6" ht="30" customHeight="1">
-      <c r="B48" s="78" t="s">
+      <c r="B48" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C48" s="78" t="s">
+      <c r="C48" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="D48" s="78" t="s">
+      <c r="D48" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="E48" s="78" t="s">
+      <c r="E48" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="F48" s="78" t="s">
+      <c r="F48" s="31" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="30" customHeight="1">
-      <c r="B49" s="78" t="s">
+      <c r="B49" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C49" s="78" t="s">
+      <c r="C49" s="31" t="s">
         <v>300</v>
       </c>
-      <c r="D49" s="78" t="s">
+      <c r="D49" s="31" t="s">
         <v>301</v>
       </c>
-      <c r="E49" s="78" t="s">
+      <c r="E49" s="31" t="s">
         <v>302</v>
       </c>
-      <c r="F49" s="78" t="s">
+      <c r="F49" s="31" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="50" spans="2:6" ht="30" customHeight="1">
-      <c r="B50" s="78" t="s">
+      <c r="B50" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C50" s="78" t="s">
+      <c r="C50" s="31" t="s">
         <v>304</v>
       </c>
-      <c r="D50" s="78" t="s">
+      <c r="D50" s="31" t="s">
         <v>305</v>
       </c>
-      <c r="E50" s="78" t="s">
+      <c r="E50" s="31" t="s">
         <v>306</v>
       </c>
-      <c r="F50" s="78" t="s">
+      <c r="F50" s="31" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="30" customHeight="1">
-      <c r="B51" s="78" t="s">
+      <c r="B51" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C51" s="78" t="s">
+      <c r="C51" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D51" s="78" t="s">
+      <c r="D51" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="E51" s="78" t="s">
+      <c r="E51" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="F51" s="78" t="s">
+      <c r="F51" s="31" t="s">
         <v>311</v>
       </c>
     </row>
@@ -10606,48 +10629,48 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="30" customHeight="1">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
     </row>
     <row r="3" spans="2:16" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="33"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="40"/>
       <c r="J3" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="K3" s="85" t="s">
+      <c r="K3" s="55" t="s">
         <v>385</v>
       </c>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="49"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="57"/>
     </row>
     <row r="4" spans="2:16" ht="18" customHeight="1">
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="33"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="40"/>
     </row>
     <row r="5" spans="2:16" ht="31.5" customHeight="1">
       <c r="B5" s="10" t="s">
@@ -10673,19 +10696,19 @@
       </c>
     </row>
     <row r="6" spans="2:16" ht="24.95" customHeight="1">
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="C6" s="78" t="s">
+      <c r="C6" s="31" t="s">
         <v>313</v>
       </c>
-      <c r="D6" s="77">
+      <c r="D6" s="30">
         <v>3</v>
       </c>
-      <c r="E6" s="77">
+      <c r="E6" s="30">
         <v>4</v>
       </c>
-      <c r="F6" s="77">
+      <c r="F6" s="30">
         <v>5</v>
       </c>
       <c r="G6" s="5">
@@ -10697,19 +10720,19 @@
       </c>
     </row>
     <row r="7" spans="2:16" ht="24.95" customHeight="1">
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="78" t="s">
+      <c r="C7" s="31" t="s">
         <v>315</v>
       </c>
-      <c r="D7" s="77">
+      <c r="D7" s="30">
         <v>2</v>
       </c>
-      <c r="E7" s="77">
+      <c r="E7" s="30">
         <v>5</v>
       </c>
-      <c r="F7" s="77">
+      <c r="F7" s="30">
         <v>3.5</v>
       </c>
       <c r="G7" s="5">
@@ -10721,19 +10744,19 @@
       </c>
     </row>
     <row r="8" spans="2:16" ht="24.95" customHeight="1">
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="C8" s="78" t="s">
+      <c r="C8" s="31" t="s">
         <v>316</v>
       </c>
-      <c r="D8" s="77">
+      <c r="D8" s="30">
         <v>2</v>
       </c>
-      <c r="E8" s="77">
+      <c r="E8" s="30">
         <v>5</v>
       </c>
-      <c r="F8" s="77">
+      <c r="F8" s="30">
         <v>4</v>
       </c>
       <c r="G8" s="5">
@@ -10745,19 +10768,19 @@
       </c>
     </row>
     <row r="9" spans="2:16" ht="24.95" customHeight="1">
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="C9" s="78" t="s">
+      <c r="C9" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="D9" s="77">
+      <c r="D9" s="30">
         <v>5</v>
       </c>
-      <c r="E9" s="77">
+      <c r="E9" s="30">
         <v>1</v>
       </c>
-      <c r="F9" s="77">
+      <c r="F9" s="30">
         <v>4</v>
       </c>
       <c r="G9" s="5">
@@ -10769,19 +10792,19 @@
       </c>
     </row>
     <row r="10" spans="2:16" ht="24.95" customHeight="1">
-      <c r="B10" s="78" t="s">
+      <c r="B10" s="31" t="s">
         <v>312</v>
       </c>
-      <c r="C10" s="78" t="s">
+      <c r="C10" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="D10" s="77">
+      <c r="D10" s="30">
         <v>3</v>
       </c>
-      <c r="E10" s="77">
+      <c r="E10" s="30">
         <v>4</v>
       </c>
-      <c r="F10" s="77">
+      <c r="F10" s="30">
         <v>4</v>
       </c>
       <c r="G10" s="5">
@@ -10793,19 +10816,19 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="24.95" customHeight="1">
-      <c r="B11" s="78" t="s">
+      <c r="B11" s="31" t="s">
         <v>278</v>
       </c>
-      <c r="C11" s="78" t="s">
+      <c r="C11" s="31" t="s">
         <v>319</v>
       </c>
-      <c r="D11" s="77">
+      <c r="D11" s="30">
         <v>2</v>
       </c>
-      <c r="E11" s="77">
+      <c r="E11" s="30">
         <v>4</v>
       </c>
-      <c r="F11" s="77">
+      <c r="F11" s="30">
         <v>2.5</v>
       </c>
       <c r="G11" s="5">
@@ -10817,19 +10840,19 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="24.95" customHeight="1">
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="C12" s="78" t="s">
+      <c r="C12" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="D12" s="77">
+      <c r="D12" s="30">
         <v>2</v>
       </c>
-      <c r="E12" s="77">
+      <c r="E12" s="30">
         <v>5</v>
       </c>
-      <c r="F12" s="77">
+      <c r="F12" s="30">
         <v>3</v>
       </c>
       <c r="G12" s="5">
@@ -10841,19 +10864,19 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="24.95" customHeight="1">
-      <c r="B13" s="78" t="s">
+      <c r="B13" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="C13" s="78" t="s">
+      <c r="C13" s="31" t="s">
         <v>322</v>
       </c>
-      <c r="D13" s="77">
+      <c r="D13" s="30">
         <v>2</v>
       </c>
-      <c r="E13" s="77">
+      <c r="E13" s="30">
         <v>5</v>
       </c>
-      <c r="F13" s="77">
+      <c r="F13" s="30">
         <v>3.5</v>
       </c>
       <c r="G13" s="5">
@@ -10865,19 +10888,19 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="24.95" customHeight="1">
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="C14" s="78" t="s">
+      <c r="C14" s="31" t="s">
         <v>324</v>
       </c>
-      <c r="D14" s="77">
+      <c r="D14" s="30">
         <v>1</v>
       </c>
-      <c r="E14" s="77">
+      <c r="E14" s="30">
         <v>5</v>
       </c>
-      <c r="F14" s="77">
+      <c r="F14" s="30">
         <v>3</v>
       </c>
       <c r="G14" s="5">
@@ -10889,19 +10912,19 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="24.95" customHeight="1">
-      <c r="B15" s="78" t="s">
+      <c r="B15" s="31" t="s">
         <v>325</v>
       </c>
-      <c r="C15" s="78" t="s">
+      <c r="C15" s="31" t="s">
         <v>326</v>
       </c>
-      <c r="D15" s="77">
+      <c r="D15" s="30">
         <v>1</v>
       </c>
-      <c r="E15" s="77">
+      <c r="E15" s="30">
         <v>5</v>
       </c>
-      <c r="F15" s="77">
+      <c r="F15" s="30">
         <v>4</v>
       </c>
       <c r="G15" s="5">
@@ -10913,19 +10936,19 @@
       </c>
     </row>
     <row r="16" spans="2:16" ht="24.95" customHeight="1">
-      <c r="B16" s="78" t="s">
+      <c r="B16" s="31" t="s">
         <v>327</v>
       </c>
-      <c r="C16" s="78" t="s">
+      <c r="C16" s="31" t="s">
         <v>328</v>
       </c>
-      <c r="D16" s="77">
+      <c r="D16" s="30">
         <v>2</v>
       </c>
-      <c r="E16" s="77">
+      <c r="E16" s="30">
         <v>5</v>
       </c>
-      <c r="F16" s="77">
+      <c r="F16" s="30">
         <v>3.5</v>
       </c>
       <c r="G16" s="5">
@@ -10937,19 +10960,19 @@
       </c>
     </row>
     <row r="17" spans="2:8" ht="24.95" customHeight="1">
-      <c r="B17" s="78" t="s">
+      <c r="B17" s="31" t="s">
         <v>329</v>
       </c>
-      <c r="C17" s="78" t="s">
+      <c r="C17" s="31" t="s">
         <v>330</v>
       </c>
-      <c r="D17" s="77">
+      <c r="D17" s="30">
         <v>2</v>
       </c>
-      <c r="E17" s="77">
+      <c r="E17" s="30">
         <v>5</v>
       </c>
-      <c r="F17" s="77">
+      <c r="F17" s="30">
         <v>3.5</v>
       </c>
       <c r="G17" s="5">
@@ -10961,19 +10984,19 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="24.95" customHeight="1">
-      <c r="B18" s="78" t="s">
+      <c r="B18" s="31" t="s">
         <v>331</v>
       </c>
-      <c r="C18" s="78" t="s">
+      <c r="C18" s="31" t="s">
         <v>332</v>
       </c>
-      <c r="D18" s="77">
+      <c r="D18" s="30">
         <v>4</v>
       </c>
-      <c r="E18" s="77">
+      <c r="E18" s="30">
         <v>2</v>
       </c>
-      <c r="F18" s="77">
+      <c r="F18" s="30">
         <v>4</v>
       </c>
       <c r="G18" s="5">
@@ -10985,19 +11008,19 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="24.95" customHeight="1">
-      <c r="B19" s="78" t="s">
+      <c r="B19" s="31" t="s">
         <v>333</v>
       </c>
-      <c r="C19" s="78" t="s">
+      <c r="C19" s="31" t="s">
         <v>334</v>
       </c>
-      <c r="D19" s="77">
+      <c r="D19" s="30">
         <v>2</v>
       </c>
-      <c r="E19" s="77">
+      <c r="E19" s="30">
         <v>4</v>
       </c>
-      <c r="F19" s="77">
+      <c r="F19" s="30">
         <v>3</v>
       </c>
       <c r="G19" s="5">
@@ -11056,16 +11079,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="49"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="33"/>
+      <c r="C3" s="40"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1">
       <c r="B4" s="1" t="s">
@@ -11079,7 +11102,7 @@
       <c r="B5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="82" t="s">
+      <c r="C5" s="34" t="s">
         <v>359</v>
       </c>
     </row>
@@ -11100,10 +11123,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="51"/>
+      <c r="C9" s="64"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
       <c r="B10" s="27" t="s">
@@ -11112,22 +11135,22 @@
       <c r="C10" s="28"/>
     </row>
     <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="44" t="s">
         <v>340</v>
       </c>
-      <c r="C11" s="38"/>
+      <c r="C11" s="45"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="79" t="s">
+      <c r="B12" s="58" t="s">
         <v>341</v>
       </c>
-      <c r="C12" s="38"/>
+      <c r="C12" s="45"/>
     </row>
     <row r="13" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="44" t="s">
         <v>342</v>
       </c>
-      <c r="C13" s="38"/>
+      <c r="C13" s="45"/>
     </row>
     <row r="14" spans="2:3" s="29" customFormat="1" ht="25.5" customHeight="1">
       <c r="B14" s="27" t="s">
@@ -11136,115 +11159,120 @@
       <c r="C14" s="28"/>
     </row>
     <row r="15" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="44" t="s">
         <v>343</v>
       </c>
-      <c r="C15" s="38"/>
+      <c r="C15" s="45"/>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1">
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="56"/>
+      <c r="C17" s="60"/>
     </row>
     <row r="18" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B18" s="79" t="s">
+      <c r="B18" s="58" t="s">
         <v>345</v>
       </c>
-      <c r="C18" s="38"/>
+      <c r="C18" s="45"/>
     </row>
     <row r="19" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B19" s="79" t="s">
+      <c r="B19" s="58" t="s">
         <v>346</v>
       </c>
-      <c r="C19" s="38"/>
+      <c r="C19" s="45"/>
     </row>
     <row r="20" spans="1:3" s="29" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B20" s="80" t="s">
+      <c r="B20" s="32" t="s">
         <v>347</v>
       </c>
       <c r="C20" s="28"/>
     </row>
     <row r="21" spans="1:3" s="29" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B21" s="80" t="s">
+      <c r="B21" s="32" t="s">
         <v>348</v>
       </c>
       <c r="C21" s="28"/>
     </row>
     <row r="22" spans="1:3" s="29" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B22" s="80" t="s">
+      <c r="B22" s="32" t="s">
         <v>349</v>
       </c>
       <c r="C22" s="28"/>
     </row>
     <row r="23" spans="1:3" s="29" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B23" s="80" t="s">
+      <c r="B23" s="32" t="s">
         <v>350</v>
       </c>
       <c r="C23" s="28"/>
     </row>
     <row r="24" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B24" s="79" t="s">
+      <c r="B24" s="58" t="s">
         <v>351</v>
       </c>
-      <c r="C24" s="38"/>
+      <c r="C24" s="45"/>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1">
-      <c r="B26" s="53" t="s">
+      <c r="B26" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="54"/>
+      <c r="C26" s="62"/>
     </row>
     <row r="27" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B27" s="79" t="s">
+      <c r="B27" s="58" t="s">
         <v>352</v>
       </c>
-      <c r="C27" s="38"/>
+      <c r="C27" s="45"/>
     </row>
     <row r="28" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B28" s="79" t="s">
+      <c r="B28" s="58" t="s">
         <v>353</v>
       </c>
-      <c r="C28" s="38"/>
+      <c r="C28" s="45"/>
     </row>
     <row r="29" spans="1:3" s="29" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B29" s="80" t="s">
+      <c r="B29" s="32" t="s">
         <v>354</v>
       </c>
       <c r="C29" s="28"/>
     </row>
     <row r="30" spans="1:3" s="29" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B30" s="80" t="s">
+      <c r="B30" s="32" t="s">
         <v>355</v>
       </c>
       <c r="C30" s="28"/>
     </row>
     <row r="31" spans="1:3" s="29" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B31" s="80" t="s">
+      <c r="B31" s="32" t="s">
         <v>356</v>
       </c>
       <c r="C31" s="28"/>
     </row>
     <row r="32" spans="1:3" s="29" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A32" s="81"/>
-      <c r="B32" s="80" t="s">
+      <c r="A32" s="33"/>
+      <c r="B32" s="32" t="s">
         <v>357</v>
       </c>
       <c r="C32" s="28"/>
     </row>
     <row r="33" spans="1:3" s="29" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="32" t="s">
         <v>361</v>
       </c>
       <c r="C33" s="28"/>
     </row>
     <row r="34" spans="1:3" ht="25.5" customHeight="1">
-      <c r="A34" s="81"/>
-      <c r="B34" s="37"/>
-      <c r="C34" s="38"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B15:C15"/>
@@ -11255,11 +11283,6 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11288,36 +11311,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="27.75" customHeight="1">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="79" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
     </row>
     <row r="3" spans="2:16" ht="79.7" customHeight="1">
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="33"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="40"/>
     </row>
     <row r="4" spans="2:16" ht="25.5" customHeight="1">
       <c r="B4" s="12" t="s">
@@ -11370,18 +11393,20 @@
       <c r="E5" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="F5" s="84">
+      <c r="F5" s="36">
         <v>46217</v>
       </c>
-      <c r="G5" s="84">
+      <c r="G5" s="36">
         <v>46217</v>
       </c>
       <c r="H5" s="5">
         <v>1</v>
       </c>
       <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="3"/>
+      <c r="J5" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="K5" s="86"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
@@ -11398,18 +11423,20 @@
       <c r="E6" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="F6" s="84">
+      <c r="F6" s="36">
         <v>46217</v>
       </c>
-      <c r="G6" s="84">
+      <c r="G6" s="36">
         <v>46217</v>
       </c>
       <c r="H6" s="5">
         <v>1</v>
       </c>
       <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="3"/>
+      <c r="J6" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="K6" s="86"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
@@ -11426,18 +11453,20 @@
       <c r="E7" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="F7" s="84">
+      <c r="F7" s="36">
         <v>46217</v>
       </c>
-      <c r="G7" s="84">
+      <c r="G7" s="36">
         <v>46217</v>
       </c>
       <c r="H7" s="5">
         <v>1</v>
       </c>
       <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="3"/>
+      <c r="J7" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="K7" s="86"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
@@ -11454,18 +11483,20 @@
       <c r="E8" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F8" s="84">
+      <c r="F8" s="36">
         <v>46217</v>
       </c>
-      <c r="G8" s="84">
+      <c r="G8" s="36">
         <v>46217</v>
       </c>
       <c r="H8" s="5">
         <v>1</v>
       </c>
       <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="3"/>
+      <c r="J8" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="K8" s="86"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
@@ -11482,18 +11513,20 @@
       <c r="E9" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F9" s="84">
+      <c r="F9" s="36">
         <v>46217</v>
       </c>
-      <c r="G9" s="84">
+      <c r="G9" s="36">
         <v>46217</v>
       </c>
       <c r="H9" s="5">
         <v>1</v>
       </c>
       <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="3"/>
+      <c r="J9" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="K9" s="86"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
@@ -11510,18 +11543,20 @@
       <c r="E10" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F10" s="84">
+      <c r="F10" s="36">
         <v>46217</v>
       </c>
-      <c r="G10" s="84">
+      <c r="G10" s="36">
         <v>46217</v>
       </c>
       <c r="H10" s="5">
         <v>1</v>
       </c>
       <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="3"/>
+      <c r="J10" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="K10" s="86"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
     </row>
@@ -11538,19 +11573,21 @@
       <c r="E11" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F11" s="84">
+      <c r="F11" s="36">
         <v>46217</v>
       </c>
-      <c r="G11" s="84">
+      <c r="G11" s="36">
         <v>46218</v>
       </c>
       <c r="H11" s="5">
         <v>2</v>
       </c>
       <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
+      <c r="J11" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="K11" s="86"/>
+      <c r="L11" s="86"/>
       <c r="M11" s="3"/>
     </row>
     <row r="12" spans="2:16" ht="30" customHeight="1">
@@ -11566,19 +11603,21 @@
       <c r="E12" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F12" s="84">
+      <c r="F12" s="36">
         <v>46217</v>
       </c>
-      <c r="G12" s="84">
+      <c r="G12" s="36">
         <v>46218</v>
       </c>
       <c r="H12" s="5">
         <v>2</v>
       </c>
       <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
+      <c r="J12" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="K12" s="86"/>
+      <c r="L12" s="86"/>
       <c r="M12" s="3"/>
     </row>
     <row r="13" spans="2:16" ht="30" customHeight="1">
@@ -11594,19 +11633,21 @@
       <c r="E13" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F13" s="84">
+      <c r="F13" s="36">
         <v>46217</v>
       </c>
-      <c r="G13" s="84">
+      <c r="G13" s="36">
         <v>46218</v>
       </c>
       <c r="H13" s="5">
         <v>2</v>
       </c>
       <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
+      <c r="J13" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="K13" s="86"/>
+      <c r="L13" s="86"/>
       <c r="M13" s="3"/>
     </row>
     <row r="14" spans="2:16" ht="30" customHeight="1">
@@ -11622,19 +11663,21 @@
       <c r="E14" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F14" s="84">
+      <c r="F14" s="36">
         <v>46218</v>
       </c>
-      <c r="G14" s="84">
+      <c r="G14" s="36">
         <v>46218</v>
       </c>
       <c r="H14" s="5">
         <v>1</v>
       </c>
       <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="J14" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
+      <c r="L14" s="86"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="2:16" ht="30" customHeight="1">
@@ -11650,19 +11693,21 @@
       <c r="E15" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F15" s="84">
+      <c r="F15" s="36">
         <v>46218</v>
       </c>
-      <c r="G15" s="84">
+      <c r="G15" s="36">
         <v>46218</v>
       </c>
       <c r="H15" s="5">
         <v>1</v>
       </c>
       <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
+      <c r="J15" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
+      <c r="L15" s="86"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="2:16" ht="30" customHeight="1">
@@ -11678,21 +11723,23 @@
       <c r="E16" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F16" s="84">
+      <c r="F16" s="36">
         <v>46218</v>
       </c>
-      <c r="G16" s="84">
+      <c r="G16" s="36">
         <v>46218</v>
       </c>
       <c r="H16" s="5">
         <v>1</v>
       </c>
       <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="J16" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
+      <c r="L16" s="86"/>
       <c r="M16" s="3"/>
-      <c r="P16" s="81" t="s">
+      <c r="P16" s="33" t="s">
         <v>386</v>
       </c>
     </row>
@@ -11709,21 +11756,23 @@
       <c r="E17" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F17" s="84">
+      <c r="F17" s="36">
         <v>46218</v>
       </c>
-      <c r="G17" s="84">
+      <c r="G17" s="36">
         <v>46219</v>
       </c>
       <c r="H17" s="5">
         <v>2</v>
       </c>
       <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+      <c r="J17" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="P17" s="81" t="s">
+      <c r="L17" s="86"/>
+      <c r="M17" s="86"/>
+      <c r="P17" s="33" t="s">
         <v>387</v>
       </c>
     </row>
@@ -11740,21 +11789,23 @@
       <c r="E18" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F18" s="84">
+      <c r="F18" s="36">
         <v>46218</v>
       </c>
-      <c r="G18" s="84">
+      <c r="G18" s="36">
         <v>46219</v>
       </c>
       <c r="H18" s="5">
         <v>2</v>
       </c>
       <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
+      <c r="J18" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="P18" s="81" t="s">
+      <c r="L18" s="86"/>
+      <c r="M18" s="86"/>
+      <c r="P18" s="33" t="s">
         <v>388</v>
       </c>
     </row>
@@ -11771,21 +11822,23 @@
       <c r="E19" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F19" s="84">
+      <c r="F19" s="36">
         <v>46218</v>
       </c>
-      <c r="G19" s="84">
+      <c r="G19" s="36">
         <v>46219</v>
       </c>
       <c r="H19" s="5">
         <v>2</v>
       </c>
       <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
+      <c r="J19" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="P19" s="81" t="s">
+      <c r="L19" s="86"/>
+      <c r="M19" s="86"/>
+      <c r="P19" s="33" t="s">
         <v>389</v>
       </c>
     </row>
@@ -11802,21 +11855,23 @@
       <c r="E20" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="F20" s="84">
+      <c r="F20" s="36">
         <v>46219</v>
       </c>
-      <c r="G20" s="84">
+      <c r="G20" s="36">
         <v>46219</v>
       </c>
       <c r="H20" s="5">
         <v>1</v>
       </c>
       <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
+      <c r="J20" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="P20" s="81" t="s">
+      <c r="M20" s="86"/>
+      <c r="P20" s="33" t="s">
         <v>390</v>
       </c>
     </row>
@@ -11833,21 +11888,23 @@
       <c r="E21" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="F21" s="84">
+      <c r="F21" s="36">
         <v>46219</v>
       </c>
-      <c r="G21" s="84">
+      <c r="G21" s="36">
         <v>46219</v>
       </c>
       <c r="H21" s="5">
         <v>1</v>
       </c>
       <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+      <c r="J21" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="P21" s="81" t="s">
+      <c r="M21" s="86"/>
+      <c r="P21" s="33" t="s">
         <v>391</v>
       </c>
     </row>
@@ -11864,20 +11921,22 @@
       <c r="E22" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F22" s="84">
+      <c r="F22" s="36">
         <v>46219</v>
       </c>
-      <c r="G22" s="84">
+      <c r="G22" s="36">
         <v>46219</v>
       </c>
       <c r="H22" s="5">
         <v>1</v>
       </c>
       <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
+      <c r="J22" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
+      <c r="M22" s="86"/>
     </row>
     <row r="23" spans="2:16" ht="30" customHeight="1">
       <c r="B23" s="5">
@@ -11892,20 +11951,22 @@
       <c r="E23" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="F23" s="84">
+      <c r="F23" s="36">
         <v>46219</v>
       </c>
-      <c r="G23" s="84">
+      <c r="G23" s="36">
         <v>46219</v>
       </c>
       <c r="H23" s="5">
         <v>1</v>
       </c>
       <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
+      <c r="J23" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
+      <c r="M23" s="86"/>
     </row>
     <row r="24" spans="2:16" ht="30" customHeight="1">
       <c r="B24" s="5">
@@ -11920,20 +11981,22 @@
       <c r="E24" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F24" s="84">
+      <c r="F24" s="36">
         <v>46219</v>
       </c>
-      <c r="G24" s="84">
+      <c r="G24" s="36">
         <v>46219</v>
       </c>
       <c r="H24" s="5">
         <v>1</v>
       </c>
       <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
+      <c r="J24" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
+      <c r="M24" s="86"/>
     </row>
     <row r="25" spans="2:16" ht="30" customHeight="1">
       <c r="B25" s="5">
@@ -11948,20 +12011,22 @@
       <c r="E25" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="F25" s="84">
+      <c r="F25" s="36">
         <v>46219</v>
       </c>
-      <c r="G25" s="84">
+      <c r="G25" s="36">
         <v>46219</v>
       </c>
       <c r="H25" s="5">
         <v>1</v>
       </c>
       <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
+      <c r="J25" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
+      <c r="M25" s="86"/>
     </row>
     <row r="26" spans="2:16" ht="30" customHeight="1">
       <c r="B26" s="5">
@@ -11976,189 +12041,191 @@
       <c r="E26" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="F26" s="84">
+      <c r="F26" s="36">
         <v>46219</v>
       </c>
-      <c r="G26" s="84">
+      <c r="G26" s="36">
         <v>46219.625</v>
       </c>
       <c r="H26" s="5">
         <v>1</v>
       </c>
       <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
+      <c r="J26" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
+      <c r="M26" s="86"/>
     </row>
     <row r="30" spans="2:16">
-      <c r="B30" s="59" t="s">
+      <c r="B30" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="C30" s="60"/>
+      <c r="C30" s="81"/>
     </row>
     <row r="31" spans="2:16">
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="62"/>
+      <c r="C31" s="83"/>
     </row>
     <row r="32" spans="2:16">
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="64"/>
+      <c r="C32" s="85"/>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="67" t="s">
+      <c r="B33" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="68"/>
+      <c r="C33" s="69"/>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="69" t="s">
+      <c r="B34" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="71"/>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="71" t="s">
+      <c r="B35" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="72"/>
+      <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="73" t="s">
+      <c r="B36" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="74"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="83"/>
+      <c r="C36" s="75"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="75" t="s">
+      <c r="B37" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="C37" s="76"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
     </row>
     <row r="38" spans="2:5">
-      <c r="B38" s="65" t="s">
+      <c r="B38" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="66"/>
-      <c r="D38" s="83"/>
-      <c r="E38" s="83"/>
+      <c r="C38" s="67"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
     </row>
     <row r="39" spans="2:5">
-      <c r="C39" s="83"/>
-      <c r="D39" s="83"/>
-      <c r="E39" s="83"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
     </row>
     <row r="40" spans="2:5">
-      <c r="C40" s="83"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="83"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
     </row>
     <row r="41" spans="2:5">
-      <c r="C41" s="83"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="83"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
     </row>
     <row r="42" spans="2:5">
-      <c r="C42" s="83"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="83"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="C43" s="83"/>
-      <c r="D43" s="83"/>
-      <c r="E43" s="83"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
     </row>
     <row r="44" spans="2:5">
-      <c r="C44" s="83"/>
-      <c r="D44" s="83"/>
-      <c r="E44" s="83"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="35"/>
     </row>
     <row r="45" spans="2:5">
-      <c r="C45" s="83"/>
-      <c r="D45" s="83"/>
-      <c r="E45" s="83"/>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="35"/>
     </row>
     <row r="46" spans="2:5">
-      <c r="C46" s="83"/>
-      <c r="D46" s="83"/>
-      <c r="E46" s="83"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
     </row>
     <row r="47" spans="2:5">
-      <c r="C47" s="83"/>
-      <c r="D47" s="83"/>
-      <c r="E47" s="83"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
     </row>
     <row r="48" spans="2:5">
-      <c r="C48" s="83"/>
-      <c r="D48" s="83"/>
-      <c r="E48" s="83"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="35"/>
     </row>
     <row r="49" spans="3:5">
-      <c r="C49" s="83"/>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
+      <c r="C49" s="35"/>
+      <c r="D49" s="35"/>
+      <c r="E49" s="35"/>
     </row>
     <row r="50" spans="3:5">
-      <c r="C50" s="83"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="35"/>
+      <c r="E50" s="35"/>
     </row>
     <row r="51" spans="3:5">
-      <c r="C51" s="83"/>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
+      <c r="C51" s="35"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="35"/>
     </row>
     <row r="52" spans="3:5">
-      <c r="C52" s="83"/>
-      <c r="D52" s="83"/>
-      <c r="E52" s="83"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="35"/>
     </row>
     <row r="53" spans="3:5">
-      <c r="C53" s="83"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="83"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="35"/>
     </row>
     <row r="54" spans="3:5">
-      <c r="C54" s="83"/>
-      <c r="D54" s="83"/>
-      <c r="E54" s="83"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="35"/>
     </row>
     <row r="55" spans="3:5">
-      <c r="C55" s="83"/>
-      <c r="D55" s="83"/>
-      <c r="E55" s="83"/>
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
     </row>
     <row r="56" spans="3:5">
-      <c r="C56" s="83"/>
-      <c r="D56" s="83"/>
-      <c r="E56" s="83"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
     </row>
     <row r="57" spans="3:5">
-      <c r="C57" s="83"/>
-      <c r="D57" s="83"/>
-      <c r="E57" s="83"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M26">
@@ -12195,16 +12262,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="49"/>
     </row>
     <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="33"/>
+      <c r="C3" s="40"/>
     </row>
     <row r="5" spans="2:3" ht="19.5" customHeight="1">
       <c r="B5" s="6" t="s">

--- a/서울_4반_5조.xlsx
+++ b/서울_4반_5조.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\vibecoding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A34647-2C9F-4D5F-9C95-ED2684DE07DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6B76AF-A0B2-4CAA-9C1E-439F96106756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="75" yWindow="1215" windowWidth="21600" windowHeight="11295" tabRatio="500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="394">
   <si>
     <t>실습 소재</t>
   </si>
@@ -8239,9 +8239,6 @@
     <t>게시글 검색 기능(Should)</t>
   </si>
   <si>
-    <t>축제 캘린더 구현(Should)</t>
-  </si>
-  <si>
     <t>지도 시각화(Should)</t>
   </si>
   <si>
@@ -8266,25 +8263,57 @@
     <t>시연 리허설 및 최종 점검</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>축제</t>
+    <t>단위를 잘 나눠서 ASK 모드로</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>쭉 만들어달라 하지 않고</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>틀을 먼저 잡는다거나</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>기능</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 캘린더 (1순위)</t>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 기능을 끊어서 하나씩</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>commit 하나씩</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 단계씩</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>예정</t>
+  </si>
+  <si>
+    <t>완료</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도 시각화 (1순위)</t>
     </r>
     <r>
       <rPr>
@@ -8305,70 +8334,52 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">게시판 추가기능(검색) (2순위)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 시각화/ 데이터 시각화 대시보드 (예비 후보)
+      <t>게시판 추가기능(검색) (2순위)
+데이터 시각화 대시보드 (예비 후보)
 - 개발기간 3일 내 완성 가능성을 최우선으로 판단</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>단위를 잘 나눠서 ASK 모드로</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도 시각화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Should)</t>
+    </r>
     <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>쭉 만들어달라 하지 않고</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>틀을 먼저 잡는다거나</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>기능</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 기능을 끊어서 하나씩</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>commit 하나씩</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>한 단계씩</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>예정</t>
   </si>
 </sst>
 </file>
@@ -8709,13 +8720,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
@@ -8727,6 +8731,13 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="18">
@@ -8904,7 +8915,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -9010,6 +9021,9 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="17" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -9056,14 +9070,20 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -9080,14 +9100,29 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9125,32 +9160,8 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="17" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9452,10 +9463,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="43"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -9490,10 +9501,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="40"/>
+      <c r="C9" s="41"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -9544,28 +9555,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="42"/>
+      <c r="C17" s="43"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="45"/>
+      <c r="C18" s="46"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="38"/>
+      <c r="C19" s="39"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="38"/>
+      <c r="C20" s="39"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -9599,13 +9610,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
       <c r="B4" s="6" t="s">
@@ -9697,46 +9708,46 @@
     </row>
     <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="41"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9769,22 +9780,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="41"/>
     </row>
     <row r="4" spans="2:6" ht="35.65" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -10629,31 +10640,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="30" customHeight="1">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
     </row>
     <row r="3" spans="2:16" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="40"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="41"/>
       <c r="J3" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="K3" s="55" t="s">
-        <v>385</v>
+      <c r="K3" s="86" t="s">
+        <v>392</v>
       </c>
       <c r="L3" s="56"/>
       <c r="M3" s="56"/>
@@ -10662,15 +10673,15 @@
       <c r="P3" s="57"/>
     </row>
     <row r="4" spans="2:16" ht="18" customHeight="1">
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="40"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="2:16" ht="31.5" customHeight="1">
       <c r="B5" s="10" t="s">
@@ -10716,7 +10727,7 @@
         <v>40</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="24.95" customHeight="1">
@@ -10764,7 +10775,7 @@
         <v>40</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" spans="2:16" ht="24.95" customHeight="1">
@@ -11079,16 +11090,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="49"/>
+      <c r="C2" s="50"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="40"/>
+      <c r="C3" s="41"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1">
       <c r="B4" s="1" t="s">
@@ -11123,10 +11134,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="64"/>
+      <c r="C9" s="59"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
       <c r="B10" s="27" t="s">
@@ -11135,22 +11146,22 @@
       <c r="C10" s="28"/>
     </row>
     <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="45" t="s">
         <v>340</v>
       </c>
-      <c r="C11" s="45"/>
+      <c r="C11" s="46"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="61" t="s">
         <v>341</v>
       </c>
-      <c r="C12" s="45"/>
+      <c r="C12" s="46"/>
     </row>
     <row r="13" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="45" t="s">
         <v>342</v>
       </c>
-      <c r="C13" s="45"/>
+      <c r="C13" s="46"/>
     </row>
     <row r="14" spans="2:3" s="29" customFormat="1" ht="25.5" customHeight="1">
       <c r="B14" s="27" t="s">
@@ -11159,28 +11170,28 @@
       <c r="C14" s="28"/>
     </row>
     <row r="15" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="45" t="s">
         <v>343</v>
       </c>
-      <c r="C15" s="45"/>
+      <c r="C15" s="46"/>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1">
-      <c r="B17" s="59" t="s">
+      <c r="B17" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="60"/>
+      <c r="C17" s="63"/>
     </row>
     <row r="18" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="61" t="s">
         <v>345</v>
       </c>
-      <c r="C18" s="45"/>
+      <c r="C18" s="46"/>
     </row>
     <row r="19" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="61" t="s">
         <v>346</v>
       </c>
-      <c r="C19" s="45"/>
+      <c r="C19" s="46"/>
     </row>
     <row r="20" spans="1:3" s="29" customFormat="1" ht="25.5" customHeight="1">
       <c r="B20" s="32" t="s">
@@ -11207,28 +11218,28 @@
       <c r="C23" s="28"/>
     </row>
     <row r="24" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="61" t="s">
         <v>351</v>
       </c>
-      <c r="C24" s="45"/>
+      <c r="C24" s="46"/>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1">
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="62"/>
+      <c r="C26" s="65"/>
     </row>
     <row r="27" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B27" s="58" t="s">
+      <c r="B27" s="61" t="s">
         <v>352</v>
       </c>
-      <c r="C27" s="45"/>
+      <c r="C27" s="46"/>
     </row>
     <row r="28" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B28" s="58" t="s">
+      <c r="B28" s="61" t="s">
         <v>353</v>
       </c>
-      <c r="C28" s="45"/>
+      <c r="C28" s="46"/>
     </row>
     <row r="29" spans="1:3" s="29" customFormat="1" ht="25.5" customHeight="1">
       <c r="B29" s="32" t="s">
@@ -11263,16 +11274,11 @@
     </row>
     <row r="34" spans="1:3" ht="25.5" customHeight="1">
       <c r="A34" s="33"/>
-      <c r="B34" s="44"/>
-      <c r="C34" s="45"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B15:C15"/>
@@ -11283,6 +11289,11 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11311,36 +11322,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="27.75" customHeight="1">
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
     </row>
     <row r="3" spans="2:16" ht="79.7" customHeight="1">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="66" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="40"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="41"/>
     </row>
     <row r="4" spans="2:16" ht="25.5" customHeight="1">
       <c r="B4" s="12" t="s">
@@ -11404,9 +11415,9 @@
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="K5" s="86"/>
+        <v>391</v>
+      </c>
+      <c r="K5" s="37"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
@@ -11434,9 +11445,9 @@
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="K6" s="86"/>
+        <v>391</v>
+      </c>
+      <c r="K6" s="37"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
@@ -11464,9 +11475,9 @@
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="K7" s="86"/>
+        <v>390</v>
+      </c>
+      <c r="K7" s="37"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
@@ -11494,9 +11505,9 @@
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="K8" s="86"/>
+        <v>390</v>
+      </c>
+      <c r="K8" s="37"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
@@ -11524,9 +11535,9 @@
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="K9" s="86"/>
+        <v>390</v>
+      </c>
+      <c r="K9" s="37"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
@@ -11554,9 +11565,9 @@
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="K10" s="86"/>
+        <v>390</v>
+      </c>
+      <c r="K10" s="37"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
     </row>
@@ -11584,10 +11595,10 @@
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="K11" s="86"/>
-      <c r="L11" s="86"/>
+        <v>390</v>
+      </c>
+      <c r="K11" s="37"/>
+      <c r="L11" s="37"/>
       <c r="M11" s="3"/>
     </row>
     <row r="12" spans="2:16" ht="30" customHeight="1">
@@ -11614,10 +11625,10 @@
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="K12" s="86"/>
-      <c r="L12" s="86"/>
+        <v>390</v>
+      </c>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
       <c r="M12" s="3"/>
     </row>
     <row r="13" spans="2:16" ht="30" customHeight="1">
@@ -11644,10 +11655,10 @@
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="K13" s="86"/>
-      <c r="L13" s="86"/>
+        <v>390</v>
+      </c>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
       <c r="M13" s="3"/>
     </row>
     <row r="14" spans="2:16" ht="30" customHeight="1">
@@ -11674,10 +11685,10 @@
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="86"/>
+      <c r="L14" s="37"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="2:16" ht="30" customHeight="1">
@@ -11704,10 +11715,10 @@
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="86"/>
+      <c r="L15" s="37"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="2:16" ht="30" customHeight="1">
@@ -11734,13 +11745,13 @@
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K16" s="3"/>
-      <c r="L16" s="86"/>
+      <c r="L16" s="37"/>
       <c r="M16" s="3"/>
       <c r="P16" s="33" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="30" customHeight="1">
@@ -11767,13 +11778,13 @@
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K17" s="3"/>
-      <c r="L17" s="86"/>
-      <c r="M17" s="86"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
       <c r="P17" s="33" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="30" customHeight="1">
@@ -11783,8 +11794,8 @@
       <c r="C18" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>376</v>
+      <c r="D18" s="14" t="s">
+        <v>393</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>367</v>
@@ -11800,13 +11811,13 @@
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K18" s="3"/>
-      <c r="L18" s="86"/>
-      <c r="M18" s="86"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
       <c r="P18" s="33" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="30" customHeight="1">
@@ -11817,7 +11828,7 @@
         <v>60</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>367</v>
@@ -11833,13 +11844,13 @@
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K19" s="3"/>
-      <c r="L19" s="86"/>
-      <c r="M19" s="86"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="37"/>
       <c r="P19" s="33" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="30" customHeight="1">
@@ -11850,7 +11861,7 @@
         <v>62</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>363</v>
@@ -11866,13 +11877,13 @@
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
-      <c r="M20" s="86"/>
+      <c r="M20" s="37"/>
       <c r="P20" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="2:16" ht="30" customHeight="1">
@@ -11883,7 +11894,7 @@
         <v>62</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>363</v>
@@ -11899,13 +11910,13 @@
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="86"/>
+      <c r="M21" s="37"/>
       <c r="P21" s="33" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="30" customHeight="1">
@@ -11916,7 +11927,7 @@
         <v>61</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>367</v>
@@ -11932,11 +11943,11 @@
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
-      <c r="M22" s="86"/>
+      <c r="M22" s="37"/>
     </row>
     <row r="23" spans="2:16" ht="30" customHeight="1">
       <c r="B23" s="5">
@@ -11946,7 +11957,7 @@
         <v>63</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>363</v>
@@ -11962,11 +11973,11 @@
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
-      <c r="M23" s="86"/>
+      <c r="M23" s="37"/>
     </row>
     <row r="24" spans="2:16" ht="30" customHeight="1">
       <c r="B24" s="5">
@@ -11976,7 +11987,7 @@
         <v>63</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>367</v>
@@ -11992,11 +12003,11 @@
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
-      <c r="M24" s="86"/>
+      <c r="M24" s="37"/>
     </row>
     <row r="25" spans="2:16" ht="30" customHeight="1">
       <c r="B25" s="5">
@@ -12006,7 +12017,7 @@
         <v>64</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>363</v>
@@ -12022,11 +12033,11 @@
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
-      <c r="M25" s="86"/>
+      <c r="M25" s="37"/>
     </row>
     <row r="26" spans="2:16" ht="30" customHeight="1">
       <c r="B26" s="5">
@@ -12036,7 +12047,7 @@
         <v>64</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>363</v>
@@ -12052,69 +12063,69 @@
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
-      <c r="M26" s="86"/>
+      <c r="M26" s="37"/>
     </row>
     <row r="30" spans="2:16">
-      <c r="B30" s="80" t="s">
+      <c r="B30" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="C30" s="81"/>
+      <c r="C30" s="69"/>
     </row>
     <row r="31" spans="2:16">
-      <c r="B31" s="82" t="s">
+      <c r="B31" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="83"/>
+      <c r="C31" s="71"/>
     </row>
     <row r="32" spans="2:16">
-      <c r="B32" s="84" t="s">
+      <c r="B32" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="85"/>
+      <c r="C32" s="73"/>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="68" t="s">
+      <c r="B33" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="69"/>
+      <c r="C33" s="77"/>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="70" t="s">
+      <c r="B34" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="79"/>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="72" t="s">
+      <c r="B35" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="73"/>
+      <c r="C35" s="81"/>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="74" t="s">
+      <c r="B36" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="75"/>
+      <c r="C36" s="83"/>
       <c r="D36" s="35"/>
       <c r="E36" s="35"/>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="76" t="s">
+      <c r="B37" s="84" t="s">
         <v>64</v>
       </c>
-      <c r="C37" s="77"/>
+      <c r="C37" s="85"/>
       <c r="D37" s="35"/>
       <c r="E37" s="35"/>
     </row>
     <row r="38" spans="2:5">
-      <c r="B38" s="66" t="s">
+      <c r="B38" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="67"/>
+      <c r="C38" s="75"/>
       <c r="D38" s="35"/>
       <c r="E38" s="35"/>
     </row>
@@ -12215,17 +12226,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M26">
@@ -12262,16 +12273,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="49"/>
+      <c r="C2" s="50"/>
     </row>
     <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="40"/>
+      <c r="C3" s="41"/>
     </row>
     <row r="5" spans="2:3" ht="19.5" customHeight="1">
       <c r="B5" s="6" t="s">

--- a/서울_4반_5조.xlsx
+++ b/서울_4반_5조.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\vibecoding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6B76AF-A0B2-4CAA-9C1E-439F96106756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187052D1-D64A-42A6-B19F-89C5938F2A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="75" yWindow="1215" windowWidth="21600" windowHeight="11295" tabRatio="500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2955" yWindow="2490" windowWidth="21600" windowHeight="11295" tabRatio="500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="395">
   <si>
     <t>실습 소재</t>
   </si>
@@ -8380,6 +8380,9 @@
       <t>(Should)</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행중</t>
   </si>
 </sst>
 </file>
@@ -11475,7 +11478,7 @@
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K7" s="37"/>
       <c r="L7" s="3"/>
@@ -11505,7 +11508,7 @@
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K8" s="37"/>
       <c r="L8" s="3"/>
@@ -11535,7 +11538,7 @@
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K9" s="37"/>
       <c r="L9" s="3"/>
@@ -11565,7 +11568,7 @@
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K10" s="37"/>
       <c r="L10" s="3"/>
@@ -11595,7 +11598,7 @@
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K11" s="37"/>
       <c r="L11" s="37"/>
@@ -11625,7 +11628,7 @@
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="K12" s="37"/>
       <c r="L12" s="37"/>
@@ -11655,7 +11658,7 @@
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K13" s="37"/>
       <c r="L13" s="37"/>
@@ -11685,7 +11688,7 @@
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="37"/>
@@ -11715,7 +11718,7 @@
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="37"/>
@@ -11745,7 +11748,7 @@
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="37"/>
@@ -11811,7 +11814,7 @@
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="37"/>
@@ -11844,7 +11847,7 @@
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="37"/>
